--- a/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFR.xlsx
+++ b/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFR.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10CB73C-AEEA-45C3-8A29-02B2DB7E47E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04DE8C8-F9D4-467F-83CB-94A169C6861E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="CAOUser" sheetId="8" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="CAOUser" sheetId="8" r:id="rId2"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId3"/>
     <sheet name="AppName" sheetId="5" r:id="rId4"/>
     <sheet name="ModuleName" sheetId="6" r:id="rId5"/>
     <sheet name="AddContact" sheetId="3" r:id="rId6"/>
@@ -1004,6 +1004,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1241,81 +1316,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
   <dimension ref="A1:A2"/>

--- a/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFR.xlsx
+++ b/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04DE8C8-F9D4-467F-83CB-94A169C6861E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1531CC11-B27F-440C-892C-58F5252555F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="85">
   <si>
     <t>Client</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t>Legal Hold test Notes</t>
+  </si>
+  <si>
+    <t>LocationBenefit</t>
+  </si>
+  <si>
+    <t>Benefit is likely &gt;75% outside the US</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -1113,7 +1119,7 @@
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,8 +1216,11 @@
       <c r="AF1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1307,6 +1316,9 @@
       </c>
       <c r="AF2" t="s">
         <v>59</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
